--- a/inasistencias-7b/alumnos-7b.xlsx
+++ b/inasistencias-7b/alumnos-7b.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="asisstencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="102">
   <si>
     <t xml:space="preserve">Nro</t>
   </si>
@@ -113,6 +113,9 @@
     <t xml:space="preserve">48296237@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
     <t xml:space="preserve">David Alejandro</t>
   </si>
   <si>
@@ -260,9 +263,6 @@
     <t xml:space="preserve">alejosuarezescuela@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marcos Ulises</t>
   </si>
   <si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t xml:space="preserve">1-uml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recup</t>
   </si>
   <si>
     <t xml:space="preserve">2-DA</t>
@@ -411,7 +414,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -433,10 +436,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -680,9 +679,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.43"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="31.19"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="8.69"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="18" min="6" style="1" width="8.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16343" min="16343" style="0" width="10.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16344" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="27" min="6" style="1" width="8.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16343" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -777,7 +775,7 @@
         <v>46184</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>46191</v>
+        <v>46167</v>
       </c>
       <c r="AD2" s="3" t="n">
         <v>46198</v>
@@ -944,7 +942,10 @@
         <f aca="false">ROUND((V3+W3/2+X3/4)*10/Z3,0)</f>
         <v>4</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1024,8 +1025,11 @@
         <f aca="false">ROUND((V4+W4/2+X4/4)*10/Z4,0)</f>
         <v>6</v>
       </c>
-      <c r="AB4" s="6" t="s">
+      <c r="AB4" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1095,7 +1099,10 @@
         <f aca="false">ROUND((V5+W5/2+X5/4)*10/Z5,0)</f>
         <v>10</v>
       </c>
-      <c r="AB5" s="6" t="s">
+      <c r="AB5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1169,7 +1176,10 @@
         <f aca="false">ROUND((V6+W6/2+X6/4)*10/Z6,0)</f>
         <v>7</v>
       </c>
-      <c r="AB6" s="6" t="s">
+      <c r="AB6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1243,8 +1253,11 @@
         <f aca="false">ROUND((V7+W7/2+X7/4)*10/Z7,0)</f>
         <v>5</v>
       </c>
-      <c r="AB7" s="6" t="s">
-        <v>14</v>
+      <c r="AB7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1252,13 +1265,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>14</v>
@@ -1314,8 +1327,11 @@
         <f aca="false">ROUND((V8+W8/2+X8/4)*10/Z8,0)</f>
         <v>9</v>
       </c>
-      <c r="AB8" s="6" t="s">
-        <v>14</v>
+      <c r="AB8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1323,13 +1339,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -1388,7 +1404,10 @@
         <f aca="false">ROUND((V9+W9/2+X9/4)*10/Z9,0)</f>
         <v>5</v>
       </c>
-      <c r="AB9" s="6" t="s">
+      <c r="AB9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1397,13 +1416,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>14</v>
@@ -1459,7 +1478,10 @@
         <f aca="false">ROUND((V10+W10/2+X10/4)*10/Z10,0)</f>
         <v>8</v>
       </c>
-      <c r="AB10" s="6" t="s">
+      <c r="AB10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC10" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1468,13 +1490,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>14</v>
@@ -1530,7 +1552,10 @@
         <f aca="false">ROUND((V11+W11/2+X11/4)*10/Z11,0)</f>
         <v>10</v>
       </c>
-      <c r="AB11" s="6" t="s">
+      <c r="AB11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC11" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1539,13 +1564,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>14</v>
@@ -1604,8 +1629,11 @@
         <f aca="false">ROUND((V12+W12/2+X12/4)*10/Z12,0)</f>
         <v>9</v>
       </c>
-      <c r="AB12" s="6" t="s">
-        <v>14</v>
+      <c r="AB12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1613,13 +1641,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>14</v>
@@ -1678,8 +1706,11 @@
         <f aca="false">ROUND((V13+W13/2+X13/4)*10/Z13,0)</f>
         <v>6</v>
       </c>
-      <c r="AB13" s="6" t="s">
-        <v>14</v>
+      <c r="AB13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1687,13 +1718,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>14</v>
@@ -1749,7 +1780,10 @@
         <f aca="false">ROUND((V14+W14/2+X14/4)*10/Z14,0)</f>
         <v>9</v>
       </c>
-      <c r="AB14" s="6" t="s">
+      <c r="AB14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC14" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1758,13 +1792,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>14</v>
@@ -1823,8 +1857,11 @@
         <f aca="false">ROUND((V15+W15/2+X15/4)*10/Z15,0)</f>
         <v>7</v>
       </c>
-      <c r="AB15" s="6" t="s">
-        <v>14</v>
+      <c r="AB15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC15" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1832,13 +1869,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>14</v>
@@ -1894,7 +1931,10 @@
         <f aca="false">ROUND((V16+W16/2+X16/4)*10/Z16,0)</f>
         <v>8</v>
       </c>
-      <c r="AB16" s="6" t="s">
+      <c r="AB16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC16" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1903,13 +1943,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>14</v>
@@ -1939,7 +1979,7 @@
         <v>16</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>14</v>
@@ -1974,8 +2014,11 @@
         <f aca="false">ROUND((V17+W17/2+X17/4)*10/Z17,0)</f>
         <v>7</v>
       </c>
-      <c r="AB17" s="6" t="s">
+      <c r="AB17" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="AC17" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1983,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>14</v>
@@ -2045,7 +2088,10 @@
         <f aca="false">ROUND((V18+W18/2+X18/4)*10/Z18,0)</f>
         <v>10</v>
       </c>
-      <c r="AB18" s="6" t="s">
+      <c r="AB18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2054,13 +2100,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>15</v>
@@ -2125,7 +2171,10 @@
         <f aca="false">ROUND((V19+W19/2+X19/4)*10/Z19,0)</f>
         <v>2</v>
       </c>
-      <c r="AB19" s="6" t="s">
+      <c r="AB19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC19" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2134,13 +2183,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>14</v>
@@ -2196,7 +2245,10 @@
         <f aca="false">ROUND((V20+W20/2+X20/4)*10/Z20,0)</f>
         <v>10</v>
       </c>
-      <c r="AB20" s="6" t="s">
+      <c r="AB20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC20" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2205,13 +2257,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>14</v>
@@ -2267,7 +2319,10 @@
         <f aca="false">ROUND((V21+W21/2+X21/4)*10/Z21,0)</f>
         <v>8</v>
       </c>
-      <c r="AB21" s="6" t="s">
+      <c r="AB21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC21" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2276,13 +2331,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>14</v>
@@ -2338,7 +2393,10 @@
         <f aca="false">ROUND((V22+W22/2+X22/4)*10/Z22,0)</f>
         <v>10</v>
       </c>
-      <c r="AB22" s="6" t="s">
+      <c r="AB22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC22" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2347,13 +2405,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>14</v>
@@ -2368,7 +2426,7 @@
         <v>14</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>0.680555555555556</v>
@@ -2421,7 +2479,10 @@
         <f aca="false">ROUND((V23+W23/2+X23/4)*10/Z23,0)</f>
         <v>5</v>
       </c>
-      <c r="AB23" s="6" t="s">
+      <c r="AB23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC23" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2492,8 +2553,11 @@
         <f aca="false">ROUND((V24+W24/2+X24/4)*10/Z24,0)</f>
         <v>8</v>
       </c>
-      <c r="AB24" s="6" t="s">
-        <v>14</v>
+      <c r="AB24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2566,8 +2630,11 @@
         <f aca="false">ROUND((V25+W25/2+X25/4)*10/Z25,0)</f>
         <v>7</v>
       </c>
-      <c r="AB25" s="6" t="s">
-        <v>14</v>
+      <c r="AB25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC25" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2640,8 +2707,11 @@
         <f aca="false">ROUND((V26+W26/2+X26/4)*10/Z26,0)</f>
         <v>7</v>
       </c>
-      <c r="AB26" s="6" t="s">
-        <v>14</v>
+      <c r="AB26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC26" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2687,7 +2757,6 @@
         <f aca="false">COUNTIF(R3:R26,"P")</f>
         <v>12</v>
       </c>
-      <c r="S27" s="1"/>
       <c r="T27" s="1" t="n">
         <f aca="false">COUNTIF(T3:T26,"P")</f>
         <v>13</v>
@@ -2695,6 +2764,10 @@
       <c r="AB27" s="1" t="n">
         <f aca="false">COUNTIF(AB3:AB26,"P")</f>
         <v>21</v>
+      </c>
+      <c r="AC27" s="1" t="n">
+        <f aca="false">COUNTIF(AC3:AC26,"P")</f>
+        <v>14</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2749,6 +2822,10 @@
         <f aca="false">COUNTIF(AB3:AB26,"M")</f>
         <v>0</v>
       </c>
+      <c r="AC28" s="1" t="n">
+        <f aca="false">COUNTIF(AC3:AC26,"M")</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
@@ -2799,6 +2876,10 @@
         <f aca="false">COUNTIF(AB3:AB26,"T")</f>
         <v>0</v>
       </c>
+      <c r="AC29" s="1" t="n">
+        <f aca="false">COUNTIF(AC3:AC26,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
@@ -2848,6 +2929,10 @@
       <c r="AB30" s="1" t="n">
         <f aca="false">SUM(AB27:AB29)</f>
         <v>21</v>
+      </c>
+      <c r="AC30" s="1" t="n">
+        <f aca="false">SUM(AC27:AC29)</f>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2878,12 +2963,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD30"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr defaultColWidth="9.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16337" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="4" min="4" style="0" width="9.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="6" min="6" style="0" width="9.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="8" min="8" style="0" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16340" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2906,13 +2994,20 @@
         <v>93</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>95</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2925,21 +3020,24 @@
       <c r="C3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="D3" s="5"/>
       <c r="E3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C3,D3,E3,F3),0)</f>
+      <c r="J3" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C3,E3,G3,I3),0)</f>
         <v>2</v>
       </c>
-      <c r="H3" s="5" t="str">
-        <f aca="false">IF(G3&gt;6,"TEA",IF(G3&gt;3,"TEP","TED"))</f>
+      <c r="K3" s="5" t="str">
+        <f aca="false">IF(J3&gt;6,"TEA",IF(J3&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
     </row>
@@ -2953,21 +3051,24 @@
       <c r="C4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>9</v>
-      </c>
+      <c r="D4" s="5"/>
       <c r="E4" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="H4" s="5"/>
+      <c r="I4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C4,D4,E4,F4),0)</f>
-        <v>7</v>
-      </c>
-      <c r="H4" s="5" t="str">
-        <f aca="false">IF(G4&gt;6,"TEA",IF(G4&gt;3,"TEP","TED"))</f>
+      <c r="J4" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C4,E4,G4,I4),0)</f>
+        <v>7</v>
+      </c>
+      <c r="K4" s="5" t="str">
+        <f aca="false">IF(J4&gt;6,"TEA",IF(J4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -2981,21 +3082,24 @@
       <c r="C5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>8</v>
-      </c>
+      <c r="D5" s="5"/>
       <c r="E5" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>10</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F5" s="5"/>
       <c r="G5" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C5,D5,E5,F5),0)</f>
-        <v>7</v>
-      </c>
-      <c r="H5" s="5" t="str">
-        <f aca="false">IF(G5&gt;6,"TEA",IF(G5&gt;3,"TEP","TED"))</f>
+        <v>7</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C5,E5,G5,I5),0)</f>
+        <v>7</v>
+      </c>
+      <c r="K5" s="5" t="str">
+        <f aca="false">IF(J5&gt;6,"TEA",IF(J5&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3009,25 +3113,28 @@
       <c r="C6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>7</v>
-      </c>
+      <c r="F6" s="5"/>
       <c r="G6" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C6,D6,E6,F6),0)</f>
+        <v>8</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C6,E6,G6,I6),0)</f>
         <v>6</v>
       </c>
-      <c r="H6" s="5" t="str">
-        <f aca="false">IF(G6&gt;6,"TEA",IF(G6&gt;3,"TEP","TED"))</f>
+      <c r="K6" s="5" t="str">
+        <f aca="false">IF(J6&gt;6,"TEA",IF(J6&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
     </row>
-    <row r="7" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
@@ -3037,26 +3144,26 @@
       <c r="C7" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="D7" s="5"/>
       <c r="E7" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C7,D7,E7,F7),0)</f>
-        <v>8</v>
-      </c>
-      <c r="H7" s="5" t="str">
-        <f aca="false">IF(G7&gt;6,"TEA",IF(G7&gt;3,"TEP","TED"))</f>
+      <c r="J7" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C7,E7,G7,I7),0)</f>
+        <v>8</v>
+      </c>
+      <c r="K7" s="5" t="str">
+        <f aca="false">IF(J7&gt;6,"TEA",IF(J7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -3077,38 +3184,40 @@
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
-      <c r="XFD7" s="1"/>
-    </row>
-    <row r="8" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+    </row>
+    <row r="8" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>9</v>
-      </c>
+      <c r="D8" s="5"/>
       <c r="E8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F8" s="5"/>
       <c r="G8" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C8,D8,E8,F8),0)</f>
+        <v>1</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C8,E8,G8,I8),0)</f>
         <v>5</v>
       </c>
-      <c r="H8" s="5" t="str">
-        <f aca="false">IF(G8&gt;6,"TEA",IF(G8&gt;3,"TEP","TED"))</f>
+      <c r="K8" s="5" t="str">
+        <f aca="false">IF(J8&gt;6,"TEA",IF(J8&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -3129,34 +3238,43 @@
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
-      <c r="XFD8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>46177</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="I9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C9,D9,E9,F9),0)</f>
-        <v>3</v>
-      </c>
-      <c r="H9" s="5" t="str">
-        <f aca="false">IF(G9&gt;6,"TEA",IF(G9&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
+      <c r="J9" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C9,E9,G9,I9),0)</f>
+        <v>6</v>
+      </c>
+      <c r="K9" s="5" t="str">
+        <f aca="false">IF(J9&gt;6,"TEA",IF(J9&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3164,26 +3282,29 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>9</v>
-      </c>
+      <c r="D10" s="5"/>
       <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F10" s="5"/>
       <c r="G10" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C10,D10,E10,F10),0)</f>
-        <v>7</v>
-      </c>
-      <c r="H10" s="5" t="str">
-        <f aca="false">IF(G10&gt;6,"TEA",IF(G10&gt;3,"TEP","TED"))</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C10,E10,G10,I10),0)</f>
+        <v>7</v>
+      </c>
+      <c r="K10" s="5" t="str">
+        <f aca="false">IF(J10&gt;6,"TEA",IF(J10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3192,26 +3313,29 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>7</v>
-      </c>
+      <c r="D11" s="5"/>
       <c r="E11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C11,D11,E11,F11),0)</f>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C11,E11,G11,I11),0)</f>
         <v>6</v>
       </c>
-      <c r="H11" s="5" t="str">
-        <f aca="false">IF(G11&gt;6,"TEA",IF(G11&gt;3,"TEP","TED"))</f>
+      <c r="K11" s="5" t="str">
+        <f aca="false">IF(J11&gt;6,"TEA",IF(J11&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
     </row>
@@ -3220,26 +3344,29 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>9</v>
-      </c>
+      <c r="D12" s="5"/>
       <c r="E12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F12" s="5"/>
       <c r="G12" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C12,D12,E12,F12),0)</f>
-        <v>9</v>
-      </c>
-      <c r="H12" s="5" t="str">
-        <f aca="false">IF(G12&gt;6,"TEA",IF(G12&gt;3,"TEP","TED"))</f>
+        <v>8</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C12,E12,G12,I12),0)</f>
+        <v>9</v>
+      </c>
+      <c r="K12" s="5" t="str">
+        <f aca="false">IF(J12&gt;6,"TEA",IF(J12&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3248,26 +3375,29 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>8</v>
-      </c>
+      <c r="D13" s="5"/>
       <c r="E13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C13,D13,E13,F13),0)</f>
-        <v>7</v>
-      </c>
-      <c r="H13" s="5" t="str">
-        <f aca="false">IF(G13&gt;6,"TEA",IF(G13&gt;3,"TEP","TED"))</f>
+      <c r="J13" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C13,E13,G13,I13),0)</f>
+        <v>7</v>
+      </c>
+      <c r="K13" s="5" t="str">
+        <f aca="false">IF(J13&gt;6,"TEA",IF(J13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3276,26 +3406,29 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>9</v>
-      </c>
+      <c r="D14" s="5"/>
       <c r="E14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C14,D14,E14,F14),0)</f>
-        <v>8</v>
-      </c>
-      <c r="H14" s="5" t="str">
-        <f aca="false">IF(G14&gt;6,"TEA",IF(G14&gt;3,"TEP","TED"))</f>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C14,E14,G14,I14),0)</f>
+        <v>8</v>
+      </c>
+      <c r="K14" s="5" t="str">
+        <f aca="false">IF(J14&gt;6,"TEA",IF(J14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3304,26 +3437,29 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>9</v>
-      </c>
+      <c r="D15" s="5"/>
       <c r="E15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>7</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F15" s="5"/>
       <c r="G15" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C15,D15,E15,F15),0)</f>
-        <v>7</v>
-      </c>
-      <c r="H15" s="5" t="str">
-        <f aca="false">IF(G15&gt;6,"TEA",IF(G15&gt;3,"TEP","TED"))</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C15,E15,G15,I15),0)</f>
+        <v>7</v>
+      </c>
+      <c r="K15" s="5" t="str">
+        <f aca="false">IF(J15&gt;6,"TEA",IF(J15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3332,26 +3468,29 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>7</v>
-      </c>
+      <c r="D16" s="5"/>
       <c r="E16" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F16" s="5"/>
       <c r="G16" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C16,D16,E16,F16),0)</f>
-        <v>9</v>
-      </c>
-      <c r="H16" s="5" t="str">
-        <f aca="false">IF(G16&gt;6,"TEA",IF(G16&gt;3,"TEP","TED"))</f>
+        <v>9</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C16,E16,G16,I16),0)</f>
+        <v>9</v>
+      </c>
+      <c r="K16" s="5" t="str">
+        <f aca="false">IF(J16&gt;6,"TEA",IF(J16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3360,59 +3499,62 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>8</v>
-      </c>
+      <c r="D17" s="5"/>
       <c r="E17" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F17" s="5"/>
       <c r="G17" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C17,D17,E17,F17),0)</f>
-        <v>8</v>
-      </c>
-      <c r="H17" s="5" t="str">
-        <f aca="false">IF(G17&gt;6,"TEA",IF(G17&gt;3,"TEP","TED"))</f>
+        <v>9</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17),0)</f>
+        <v>8</v>
+      </c>
+      <c r="K17" s="5" t="str">
+        <f aca="false">IF(J17&gt;6,"TEA",IF(J17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
-    <row r="18" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D18" s="5" t="n">
-        <v>7</v>
-      </c>
+      <c r="D18" s="5"/>
       <c r="E18" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="F18" s="5"/>
       <c r="G18" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C18,D18,E18,F18),0)</f>
-        <v>8</v>
-      </c>
-      <c r="H18" s="5" t="str">
-        <f aca="false">IF(G18&gt;6,"TEA",IF(G18&gt;3,"TEP","TED"))</f>
+        <v>7</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C18,E18,G18,I18),0)</f>
+        <v>8</v>
+      </c>
+      <c r="K18" s="5" t="str">
+        <f aca="false">IF(J18&gt;6,"TEA",IF(J18&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -3433,66 +3575,73 @@
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
       <c r="AE18" s="1"/>
-      <c r="XFD18" s="1"/>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="D19" s="5"/>
       <c r="E19" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="H19" s="5"/>
+      <c r="I19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C19,D19,E19,F19),0)</f>
-        <v>4</v>
-      </c>
-      <c r="H19" s="5" t="str">
-        <f aca="false">IF(G19&gt;6,"TEA",IF(G19&gt;3,"TEP","TED"))</f>
+      <c r="J19" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C19,E19,G19,I19),0)</f>
+        <v>6</v>
+      </c>
+      <c r="K19" s="5" t="str">
+        <f aca="false">IF(J19&gt;6,"TEA",IF(J19&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
     </row>
-    <row r="20" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>8</v>
-      </c>
+      <c r="D20" s="5"/>
       <c r="E20" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F20" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C20,D20,E20,F20),0)</f>
-        <v>8</v>
-      </c>
-      <c r="H20" s="5" t="str">
-        <f aca="false">IF(G20&gt;6,"TEA",IF(G20&gt;3,"TEP","TED"))</f>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C20,E20,G20,I20),0)</f>
+        <v>8</v>
+      </c>
+      <c r="K20" s="5" t="str">
+        <f aca="false">IF(J20&gt;6,"TEA",IF(J20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -3513,33 +3662,38 @@
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1"/>
-      <c r="XFD20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>8</v>
-      </c>
+      <c r="D21" s="5"/>
       <c r="E21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>8</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F21" s="5"/>
       <c r="G21" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C21,D21,E21,F21),0)</f>
+        <v>1</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C21,E21,G21,I21),0)</f>
         <v>6</v>
       </c>
-      <c r="H21" s="5" t="str">
-        <f aca="false">IF(G21&gt;6,"TEA",IF(G21&gt;3,"TEP","TED"))</f>
+      <c r="K21" s="5" t="str">
+        <f aca="false">IF(J21&gt;6,"TEA",IF(J21&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
     </row>
@@ -3548,26 +3702,29 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D22" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="D22" s="5"/>
       <c r="E22" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>10</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F22" s="5"/>
       <c r="G22" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C22,D22,E22,F22),0)</f>
-        <v>9</v>
-      </c>
-      <c r="H22" s="5" t="str">
-        <f aca="false">IF(G22&gt;6,"TEA",IF(G22&gt;3,"TEP","TED"))</f>
+        <v>8</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C22,E22,G22,I22),0)</f>
+        <v>9</v>
+      </c>
+      <c r="K22" s="5" t="str">
+        <f aca="false">IF(J22&gt;6,"TEA",IF(J22&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3576,26 +3733,29 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>9</v>
-      </c>
+      <c r="D23" s="5"/>
       <c r="E23" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F23" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C23,D23,E23,F23),0)</f>
-        <v>7</v>
-      </c>
-      <c r="H23" s="5" t="str">
-        <f aca="false">IF(G23&gt;6,"TEA",IF(G23&gt;3,"TEP","TED"))</f>
+      <c r="J23" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C23,E23,G23,I23),0)</f>
+        <v>7</v>
+      </c>
+      <c r="K23" s="5" t="str">
+        <f aca="false">IF(J23&gt;6,"TEA",IF(J23&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3609,21 +3769,24 @@
       <c r="C24" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="D24" s="5"/>
       <c r="E24" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>8</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F24" s="5"/>
       <c r="G24" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C24,D24,E24,F24),0)</f>
-        <v>9</v>
-      </c>
-      <c r="H24" s="5" t="str">
-        <f aca="false">IF(G24&gt;6,"TEA",IF(G24&gt;3,"TEP","TED"))</f>
+        <v>8</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C24,E24,G24,I24),0)</f>
+        <v>9</v>
+      </c>
+      <c r="K24" s="5" t="str">
+        <f aca="false">IF(J24&gt;6,"TEA",IF(J24&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3637,21 +3800,24 @@
       <c r="C25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>8</v>
-      </c>
+      <c r="D25" s="5"/>
       <c r="E25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F25" s="5"/>
       <c r="G25" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C25,D25,E25,F25),0)</f>
+        <v>1</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C25,E25,G25,I25),0)</f>
         <v>6</v>
       </c>
-      <c r="H25" s="5" t="str">
-        <f aca="false">IF(G25&gt;6,"TEA",IF(G25&gt;3,"TEP","TED"))</f>
+      <c r="K25" s="5" t="str">
+        <f aca="false">IF(J25&gt;6,"TEA",IF(J25&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
     </row>
@@ -3663,34 +3829,39 @@
         <v>86</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>46177</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F26" s="5"/>
       <c r="G26" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C26,D26,E26,F26),0)</f>
-        <v>6</v>
-      </c>
-      <c r="H26" s="5" t="str">
-        <f aca="false">IF(G26&gt;6,"TEA",IF(G26&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>7</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C26,E26,G26,I26),0)</f>
+        <v>7</v>
+      </c>
+      <c r="K26" s="5" t="str">
+        <f aca="false">IF(J26&gt;6,"TEA",IF(J26&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
+      <c r="A28" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
+      <c r="A30" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C3:H26">
+  <conditionalFormatting sqref="C3:K26">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -3744,16 +3915,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3856,7 +4027,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>1</v>
@@ -3870,10 +4041,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>4</v>
@@ -3887,10 +4058,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>8</v>
@@ -3904,10 +4075,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>3</v>
@@ -3921,10 +4092,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>10</v>
@@ -3938,10 +4109,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>8</v>
@@ -3960,7 +4131,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>8</v>
@@ -3968,7 +4139,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>5</v>
@@ -3979,10 +4150,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>9</v>
@@ -4001,7 +4172,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>7</v>
@@ -4012,10 +4183,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>9</v>
@@ -4029,10 +4200,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>10</v>
@@ -4046,10 +4217,10 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>9</v>
@@ -4063,10 +4234,10 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>10</v>
@@ -4085,7 +4256,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>9</v>
@@ -4093,7 +4264,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>8</v>
@@ -4101,7 +4272,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>6</v>
@@ -4109,7 +4280,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>4</v>
@@ -4120,10 +4291,10 @@
         <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>9</v>
@@ -4137,10 +4308,10 @@
         <v>18</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>9</v>
@@ -4159,7 +4330,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>4</v>
@@ -4170,10 +4341,10 @@
         <v>19</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>10</v>
@@ -4192,7 +4363,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>6</v>
@@ -4203,10 +4374,10 @@
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>7</v>
@@ -4220,10 +4391,10 @@
         <v>21</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>6</v>
@@ -4242,7 +4413,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>5</v>
@@ -4342,16 +4513,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4457,10 +4628,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>9</v>
@@ -4474,7 +4645,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>1</v>
@@ -4488,10 +4659,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>9</v>
@@ -4505,10 +4676,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>7</v>
@@ -4522,10 +4693,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>9</v>
@@ -4539,10 +4710,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>9</v>
@@ -4561,7 +4732,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>8</v>
@@ -4569,7 +4740,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>4</v>
@@ -4580,10 +4751,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -4602,7 +4773,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>8</v>
@@ -4610,7 +4781,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>8</v>
@@ -4621,10 +4792,10 @@
         <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>9</v>
@@ -4638,10 +4809,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>7</v>
@@ -4655,10 +4826,10 @@
         <v>15</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>8</v>
@@ -4672,10 +4843,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>7</v>
@@ -4694,7 +4865,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>7</v>
@@ -4705,7 +4876,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>1</v>
@@ -4719,10 +4890,10 @@
         <v>18</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>10</v>
@@ -4741,7 +4912,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>6</v>
@@ -4752,10 +4923,10 @@
         <v>19</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>8</v>
@@ -4769,10 +4940,10 @@
         <v>20</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>10</v>
@@ -4786,10 +4957,10 @@
         <v>21</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>9</v>
@@ -4808,7 +4979,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>8</v>
@@ -4908,16 +5079,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5063,7 +5234,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1</v>
@@ -5077,7 +5248,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>1</v>
@@ -5091,7 +5262,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>1</v>
@@ -5105,10 +5276,10 @@
         <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>5</v>
@@ -5122,10 +5293,10 @@
         <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>9</v>
@@ -5144,7 +5315,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>8</v>
@@ -5152,7 +5323,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>6</v>
@@ -5160,7 +5331,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>5</v>
@@ -5168,7 +5339,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>3</v>
@@ -5179,10 +5350,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>6</v>
@@ -5196,10 +5367,10 @@
         <v>12</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>7</v>
@@ -5218,7 +5389,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>6</v>
@@ -5226,7 +5397,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>4</v>
@@ -5237,7 +5408,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>1</v>
@@ -5251,10 +5422,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>9</v>
@@ -5268,10 +5439,10 @@
         <v>15</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>9</v>
@@ -5285,10 +5456,10 @@
         <v>16</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>7</v>
@@ -5302,10 +5473,10 @@
         <v>17</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>5</v>
@@ -5319,10 +5490,10 @@
         <v>18</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>7</v>
@@ -5341,7 +5512,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>3</v>
@@ -5352,7 +5523,7 @@
         <v>19</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>1</v>
@@ -5366,10 +5537,10 @@
         <v>20</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>10</v>
@@ -5388,7 +5559,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>8</v>
@@ -5396,7 +5567,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>4</v>
@@ -5407,10 +5578,10 @@
         <v>21</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>7</v>

--- a/inasistencias-7b/alumnos-7b.xlsx
+++ b/inasistencias-7b/alumnos-7b.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="asisstencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="102">
   <si>
     <t xml:space="preserve">Nro</t>
   </si>
@@ -414,7 +414,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -436,6 +436,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -778,10 +782,10 @@
         <v>46167</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>46198</v>
+        <v>46254</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>46205</v>
+        <v>46261</v>
       </c>
       <c r="AF2" s="3" t="n">
         <v>46212</v>
@@ -948,6 +952,9 @@
       <c r="AC3" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD3" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -1031,6 +1038,9 @@
       <c r="AC4" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD4" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -1105,6 +1115,9 @@
       <c r="AC5" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD5" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1182,6 +1195,9 @@
       <c r="AC6" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD6" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1259,6 +1275,9 @@
       <c r="AC7" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AD7" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1333,6 +1352,9 @@
       <c r="AC8" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="AD8" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -1410,6 +1432,9 @@
       <c r="AC9" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD9" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -1484,6 +1509,9 @@
       <c r="AC10" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD10" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -1558,6 +1586,9 @@
       <c r="AC11" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD11" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -1633,6 +1664,9 @@
         <v>14</v>
       </c>
       <c r="AC12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD12" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1712,6 +1746,9 @@
       <c r="AC13" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AD13" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -1786,6 +1823,9 @@
       <c r="AC14" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD14" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -1863,6 +1903,9 @@
       <c r="AC15" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AD15" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
@@ -1937,6 +1980,9 @@
       <c r="AC16" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD16" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2020,6 +2066,9 @@
       <c r="AC17" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AD17" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -2094,6 +2143,9 @@
       <c r="AC18" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD18" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
@@ -2177,6 +2229,9 @@
       <c r="AC19" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="AD19" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -2251,6 +2306,9 @@
       <c r="AC20" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD20" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2325,6 +2383,9 @@
       <c r="AC21" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD21" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -2399,6 +2460,9 @@
       <c r="AC22" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD22" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
@@ -2485,6 +2549,9 @@
       <c r="AC23" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AD23" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
@@ -2559,6 +2626,9 @@
       <c r="AC24" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AD24" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
@@ -2636,6 +2706,9 @@
       <c r="AC25" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="AD25" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
@@ -2713,6 +2786,9 @@
       <c r="AC26" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="AD26" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
@@ -2769,6 +2845,10 @@
         <f aca="false">COUNTIF(AC3:AC26,"P")</f>
         <v>14</v>
       </c>
+      <c r="AD27" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD26,"P")</f>
+        <v>16</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
@@ -2825,6 +2905,10 @@
       <c r="AC28" s="1" t="n">
         <f aca="false">COUNTIF(AC3:AC26,"M")</f>
         <v>5</v>
+      </c>
+      <c r="AD28" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD26,"M")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2880,6 +2964,10 @@
         <f aca="false">COUNTIF(AC3:AC26,"T")</f>
         <v>0</v>
       </c>
+      <c r="AD29" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD26,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
@@ -2933,6 +3021,10 @@
       <c r="AC30" s="1" t="n">
         <f aca="false">SUM(AC27:AC29)</f>
         <v>19</v>
+      </c>
+      <c r="AD30" s="1" t="n">
+        <f aca="false">SUM(AD27:AD29)</f>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2968,9 +3060,9 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.79"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="4" min="4" style="0" width="9.58"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="6" min="6" style="0" width="9.58"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="8" min="8" style="0" width="9.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="9.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="9.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="8" min="8" style="1" width="9.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16340" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -2999,7 +3091,6 @@
       <c r="G2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
         <v>95</v>
       </c>
@@ -3134,7 +3225,7 @@
         <v>TEP</v>
       </c>
     </row>
-    <row r="7" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
@@ -3188,7 +3279,7 @@
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
     </row>
-    <row r="8" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
@@ -3525,7 +3616,7 @@
         <v>TEA</v>
       </c>
     </row>
-    <row r="18" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
@@ -3612,7 +3703,7 @@
         <v>TEP</v>
       </c>
     </row>
-    <row r="20" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
@@ -3855,10 +3946,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
+      <c r="A28" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6"/>
+      <c r="A30" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:K26">

--- a/inasistencias-7b/alumnos-7b.xlsx
+++ b/inasistencias-7b/alumnos-7b.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="102">
   <si>
     <t xml:space="preserve">Nro</t>
   </si>
@@ -785,16 +785,16 @@
         <v>46254</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>46212</v>
+        <v>46275</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>46219</v>
+        <v>46289</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>46226</v>
+        <v>46296</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46233</v>
@@ -952,8 +952,20 @@
       <c r="AC3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD3" s="6" t="s">
-        <v>14</v>
+      <c r="AD3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH3" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1038,8 +1050,20 @@
       <c r="AC4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="6" t="s">
-        <v>14</v>
+      <c r="AD4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH4" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1115,7 +1139,19 @@
       <c r="AC5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD5" s="6" t="s">
+      <c r="AD5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH5" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1195,8 +1231,20 @@
       <c r="AC6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD6" s="6" t="s">
-        <v>15</v>
+      <c r="AD6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH6" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1275,8 +1323,20 @@
       <c r="AC7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AD7" s="6" t="s">
-        <v>14</v>
+      <c r="AD7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH7" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1352,7 +1412,19 @@
       <c r="AC8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AD8" s="6" t="s">
+      <c r="AD8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH8" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1432,7 +1504,19 @@
       <c r="AC9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD9" s="6" t="s">
+      <c r="AD9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH9" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1509,8 +1593,20 @@
       <c r="AC10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD10" s="6" t="s">
-        <v>14</v>
+      <c r="AD10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH10" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1586,7 +1682,19 @@
       <c r="AC11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD11" s="6" t="s">
+      <c r="AD11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH11" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1666,7 +1774,19 @@
       <c r="AC12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AD12" s="6" t="s">
+      <c r="AD12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH12" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1746,7 +1866,19 @@
       <c r="AC13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AD13" s="6" t="s">
+      <c r="AD13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH13" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1823,7 +1955,19 @@
       <c r="AC14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD14" s="6" t="s">
+      <c r="AD14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1903,8 +2047,20 @@
       <c r="AC15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AD15" s="6" t="s">
-        <v>14</v>
+      <c r="AD15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH15" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1980,8 +2136,20 @@
       <c r="AC16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD16" s="6" t="s">
-        <v>15</v>
+      <c r="AD16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH16" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2066,7 +2234,19 @@
       <c r="AC17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AD17" s="6" t="s">
+      <c r="AD17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH17" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2143,7 +2323,19 @@
       <c r="AC18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD18" s="6" t="s">
+      <c r="AD18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH18" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2229,8 +2421,20 @@
       <c r="AC19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AD19" s="6" t="s">
-        <v>14</v>
+      <c r="AD19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH19" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2306,8 +2510,20 @@
       <c r="AC20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD20" s="6" t="s">
-        <v>14</v>
+      <c r="AD20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH20" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2383,8 +2599,20 @@
       <c r="AC21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD21" s="6" t="s">
-        <v>14</v>
+      <c r="AD21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH21" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2460,8 +2688,20 @@
       <c r="AC22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD22" s="6" t="s">
-        <v>14</v>
+      <c r="AD22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH22" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2549,7 +2789,19 @@
       <c r="AC23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD23" s="6" t="s">
+      <c r="AD23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH23" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2626,8 +2878,20 @@
       <c r="AC24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AD24" s="6" t="s">
-        <v>15</v>
+      <c r="AD24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH24" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2706,7 +2970,19 @@
       <c r="AC25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AD25" s="6" t="s">
+      <c r="AD25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH25" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2786,7 +3062,19 @@
       <c r="AC26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AD26" s="6" t="s">
+      <c r="AD26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH26" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2849,6 +3137,22 @@
         <f aca="false">COUNTIF(AD3:AD26,"P")</f>
         <v>16</v>
       </c>
+      <c r="AE27" s="1" t="n">
+        <f aca="false">COUNTIF(AE3:AE26,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AF27" s="1" t="n">
+        <f aca="false">COUNTIF(AF3:AF26,"P")</f>
+        <v>12</v>
+      </c>
+      <c r="AG27" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG26,"P")</f>
+        <v>11</v>
+      </c>
+      <c r="AH27" s="1" t="n">
+        <f aca="false">COUNTIF(AH3:AH26,"P")</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
@@ -2908,6 +3212,22 @@
       </c>
       <c r="AD28" s="1" t="n">
         <f aca="false">COUNTIF(AD3:AD26,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AE28" s="1" t="n">
+        <f aca="false">COUNTIF(AE3:AE26,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1" t="n">
+        <f aca="false">COUNTIF(AF3:AF26,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG26,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="1" t="n">
+        <f aca="false">COUNTIF(AH3:AH26,"M")</f>
         <v>0</v>
       </c>
     </row>
@@ -2968,6 +3288,22 @@
         <f aca="false">COUNTIF(AD3:AD26,"T")</f>
         <v>0</v>
       </c>
+      <c r="AE29" s="1" t="n">
+        <f aca="false">COUNTIF(AE3:AE26,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AF29" s="1" t="n">
+        <f aca="false">COUNTIF(AF3:AF26,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AG29" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG26,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AH29" s="1" t="n">
+        <f aca="false">COUNTIF(AH3:AH26,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
@@ -3025,6 +3361,22 @@
       <c r="AD30" s="1" t="n">
         <f aca="false">SUM(AD27:AD29)</f>
         <v>16</v>
+      </c>
+      <c r="AE30" s="1" t="n">
+        <f aca="false">SUM(AE27:AE29)</f>
+        <v>20</v>
+      </c>
+      <c r="AF30" s="1" t="n">
+        <f aca="false">SUM(AF27:AF29)</f>
+        <v>12</v>
+      </c>
+      <c r="AG30" s="1" t="n">
+        <f aca="false">SUM(AG27:AG29)</f>
+        <v>11</v>
+      </c>
+      <c r="AH30" s="1" t="n">
+        <f aca="false">SUM(AH27:AH29)</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
